--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64923_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64923_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb4291da0ce3e40c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf0ea3c4480c44fcd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4131</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7921</x:v>
+        <x:v>      3.7047</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64923_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64923_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf0ea3c4480c44fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9acd2551995c44cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,741 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8517</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7211</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1384</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4151</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.1569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0381</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4798</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2857</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5383</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2471</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2121</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0676</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.2402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.8523</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6186</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.6186</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5616</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7339</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.9416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4810</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6274</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7921</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.7928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.0651</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>18/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4131</x:v>
+        <x:v>      4.6132</x:v>
       </x:c>
     </x:row>
     <x:row>
